--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,7 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -446,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.58215</v>
+        <v>16.91091</v>
       </c>
       <c r="D2" t="n">
-        <v>16.27896</v>
+        <v>15.80976</v>
       </c>
       <c r="E2" t="n">
-        <v>16.39244</v>
+        <v>15.98686</v>
       </c>
       <c r="F2" t="n">
-        <v>43.25941</v>
+        <v>22.01369</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04961</v>
+        <v>21.42634</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8053</v>
+        <v>33.69964</v>
       </c>
     </row>
     <row r="3">
@@ -475,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.11889</v>
+        <v>16.48741</v>
       </c>
       <c r="D3" t="n">
-        <v>16.58219</v>
+        <v>15.69791</v>
       </c>
       <c r="E3" t="n">
-        <v>16.51498</v>
+        <v>16.02445</v>
       </c>
       <c r="F3" t="n">
-        <v>42.79705</v>
+        <v>21.66519</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05045</v>
+        <v>21.71033</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80258</v>
+        <v>34.80416</v>
       </c>
     </row>
     <row r="4">
@@ -500,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.50391</v>
+        <v>16.81678</v>
       </c>
       <c r="D4" t="n">
-        <v>16.65109</v>
+        <v>15.6854</v>
       </c>
       <c r="E4" t="n">
-        <v>16.89806</v>
+        <v>16.2767</v>
       </c>
       <c r="F4" t="n">
-        <v>41.59363</v>
+        <v>21.41832</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05116</v>
+        <v>22.00854</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79238</v>
+        <v>33.21621</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.00746</v>
+        <v>16.6358</v>
       </c>
       <c r="D5" t="n">
-        <v>16.74438</v>
+        <v>16.08063</v>
       </c>
       <c r="E5" t="n">
-        <v>16.44615</v>
+        <v>16.10584</v>
       </c>
       <c r="F5" t="n">
-        <v>42.81017</v>
+        <v>21.21251</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05034</v>
+        <v>21.8251</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81231</v>
+        <v>33.64998</v>
       </c>
     </row>
     <row r="6">
@@ -550,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.49349</v>
+        <v>16.58858</v>
       </c>
       <c r="D6" t="n">
-        <v>16.03936</v>
+        <v>15.70638</v>
       </c>
       <c r="E6" t="n">
-        <v>16.94224</v>
+        <v>16.40178</v>
       </c>
       <c r="F6" t="n">
-        <v>42.42684</v>
+        <v>21.72233</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05044</v>
+        <v>21.84927</v>
       </c>
       <c r="H6" t="n">
-        <v>1.78016</v>
+        <v>34.35502</v>
       </c>
     </row>
     <row r="7">
@@ -575,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.58395</v>
+        <v>16.4658</v>
       </c>
       <c r="D7" t="n">
-        <v>16.70233</v>
+        <v>16.00767</v>
       </c>
       <c r="E7" t="n">
-        <v>16.67257</v>
+        <v>16.13604</v>
       </c>
       <c r="F7" t="n">
-        <v>42.26083</v>
+        <v>21.17509</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05073</v>
+        <v>21.47847</v>
       </c>
       <c r="H7" t="n">
-        <v>1.84259</v>
+        <v>34.10631</v>
       </c>
     </row>
     <row r="8">
@@ -600,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.97666</v>
+        <v>16.72907</v>
       </c>
       <c r="D8" t="n">
-        <v>16.59317</v>
+        <v>15.92891</v>
       </c>
       <c r="E8" t="n">
-        <v>16.40302</v>
+        <v>16.41095</v>
       </c>
       <c r="F8" t="n">
-        <v>41.58063</v>
+        <v>21.66187</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0503</v>
+        <v>21.68804</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80877</v>
+        <v>34.01645</v>
       </c>
     </row>
     <row r="9">
@@ -625,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.65521</v>
+        <v>16.29803</v>
       </c>
       <c r="D9" t="n">
-        <v>16.03069</v>
+        <v>15.81366</v>
       </c>
       <c r="E9" t="n">
-        <v>16.85749</v>
+        <v>16.21464</v>
       </c>
       <c r="F9" t="n">
-        <v>42.1869</v>
+        <v>20.89804</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05141</v>
+        <v>21.48915</v>
       </c>
       <c r="H9" t="n">
-        <v>1.80834</v>
+        <v>33.96391</v>
       </c>
     </row>
     <row r="10">
@@ -650,156 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.65948</v>
+        <v>16.3943</v>
       </c>
       <c r="D10" t="n">
-        <v>16.32819</v>
+        <v>16.05218</v>
       </c>
       <c r="E10" t="n">
-        <v>16.27491</v>
+        <v>16.21143</v>
       </c>
       <c r="F10" t="n">
-        <v>42.48547</v>
+        <v>21.47085</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05052</v>
+        <v>21.84361</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81867</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.6099</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.09307</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.60428</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.10162</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.61126</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.0995</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.59753</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.08457</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.59956</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.11646</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.6089</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.12224</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.61309</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.08968</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.60465</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.10129</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.60677</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.10974</v>
+        <v>33.51621</v>
       </c>
     </row>
   </sheetData>
